--- a/products/dividend-wealth-builder/Dividend_Wealth_Builder.xlsx
+++ b/products/dividend-wealth-builder/Dividend_Wealth_Builder.xlsx
@@ -435,7 +435,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
           <showPercent val="1"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
